--- a/Screening experiments/Screening.xlsx
+++ b/Screening experiments/Screening.xlsx
@@ -1,21 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ersat\CODE\CcaSolitaiRe\Screening experiments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8783A00-BED9-45F6-B445-AD6A02393E39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C213730-A778-449D-92CB-FB30785AB510}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="pKS-02-004,6" sheetId="1" r:id="rId1"/>
     <sheet name="pKS-02-014" sheetId="2" r:id="rId2"/>
     <sheet name="pKS-02-016,18" sheetId="3" r:id="rId3"/>
+    <sheet name="pKS-02-019" sheetId="4" r:id="rId4"/>
+    <sheet name="pKS-02-017" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="40">
   <si>
     <t>RED</t>
   </si>
@@ -137,6 +139,27 @@
   </si>
   <si>
     <t>STDEV</t>
+  </si>
+  <si>
+    <t>pKS-02-019-C1</t>
+  </si>
+  <si>
+    <t>pKS-02-019-C2</t>
+  </si>
+  <si>
+    <t>pKS-02-019-C3</t>
+  </si>
+  <si>
+    <t>pKS-02-019</t>
+  </si>
+  <si>
+    <t>pKS-02-017</t>
+  </si>
+  <si>
+    <t>pKS-02-017-C1</t>
+  </si>
+  <si>
+    <t>pKS-02-017-C2</t>
   </si>
 </sst>
 </file>
@@ -525,7 +548,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="en-GB"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -819,7 +842,7 @@
                 <c:order val="1"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'pKS-02-004,6'!$C$18</c15:sqref>
@@ -846,7 +869,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'pKS-02-004,6'!$A$19:$A$20</c15:sqref>
@@ -866,7 +889,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'pKS-02-004,6'!$C$19:$C$20</c15:sqref>
@@ -885,7 +908,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000001-E6B2-42E8-9117-98F4E480EB6C}"/>
                   </c:ext>
@@ -1844,7 +1867,7 @@
                 <c:order val="1"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'pKS-02-014'!$C$18</c15:sqref>
@@ -1871,7 +1894,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'pKS-02-014'!$A$19:$A$20</c15:sqref>
@@ -1891,7 +1914,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'pKS-02-014'!$C$19:$C$20</c15:sqref>
@@ -1910,7 +1933,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000002-BD68-4B4D-922B-AD51B83B22F6}"/>
                   </c:ext>
@@ -2530,7 +2553,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="en-GB"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -2929,7 +2952,7 @@
                 <c:order val="1"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'pKS-02-016,18'!$C$18</c15:sqref>
@@ -2960,7 +2983,7 @@
                   <c:noEndCap val="0"/>
                   <c:plus>
                     <c:numRef>
-                      <c:extLst>
+                      <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                         <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                           <c15:formulaRef>
                             <c15:sqref>'pKS-02-016,18'!$C$22:$C$23</c15:sqref>
@@ -2981,7 +3004,7 @@
                   </c:plus>
                   <c:minus>
                     <c:numRef>
-                      <c:extLst>
+                      <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                         <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                           <c15:formulaRef>
                             <c15:sqref>'pKS-02-016,18'!$C$22:$C$23</c15:sqref>
@@ -3016,7 +3039,7 @@
                 </c:errBars>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'pKS-02-016,18'!$A$19:$A$20</c15:sqref>
@@ -3036,7 +3059,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'pKS-02-016,18'!$C$19:$C$20</c15:sqref>
@@ -3055,7 +3078,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000001-310E-44F1-A4BC-60527F4E8F85}"/>
                   </c:ext>
@@ -8587,4 +8610,614 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C132F3F6-DC0C-4B5E-AEEA-10C5F14B376A}">
+  <dimension ref="A1:L23"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.5703125" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="8:12" x14ac:dyDescent="0.25">
+      <c r="H1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="8:12" x14ac:dyDescent="0.25">
+      <c r="H2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I2" s="4">
+        <v>5.0299999999999997E-2</v>
+      </c>
+      <c r="J2" s="5">
+        <v>1.1718</v>
+      </c>
+      <c r="K2" s="5">
+        <v>1.1644000000000001</v>
+      </c>
+      <c r="L2" s="5">
+        <v>1.1600999999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="8:12" x14ac:dyDescent="0.25">
+      <c r="H3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I3" s="4">
+        <v>111</v>
+      </c>
+      <c r="J3" s="5">
+        <v>215</v>
+      </c>
+      <c r="K3" s="5">
+        <v>222</v>
+      </c>
+      <c r="L3" s="5">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="4" spans="8:12" x14ac:dyDescent="0.25">
+      <c r="H4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I4">
+        <f>I2-$I$2</f>
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <f>J2-$I$2</f>
+        <v>1.1214999999999999</v>
+      </c>
+      <c r="K4">
+        <f t="shared" ref="K4:L4" si="0">K2-$I$2</f>
+        <v>1.1141000000000001</v>
+      </c>
+      <c r="L4">
+        <f t="shared" si="0"/>
+        <v>1.1097999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="8:12" x14ac:dyDescent="0.25">
+      <c r="H5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I5">
+        <f>I3-$I$3</f>
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <f>J3-$I$3</f>
+        <v>104</v>
+      </c>
+      <c r="K5">
+        <f>K3-$I$3</f>
+        <v>111</v>
+      </c>
+      <c r="L5">
+        <f>L3-$I$3</f>
+        <v>117</v>
+      </c>
+    </row>
+    <row r="6" spans="8:12" x14ac:dyDescent="0.25">
+      <c r="H6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I6" t="s">
+        <v>7</v>
+      </c>
+      <c r="J6">
+        <f>J5/J4</f>
+        <v>92.732946946054398</v>
+      </c>
+      <c r="K6">
+        <f t="shared" ref="K6:L6" si="1">K5/K4</f>
+        <v>99.631989947042442</v>
+      </c>
+      <c r="L6">
+        <f t="shared" si="1"/>
+        <v>105.42440079293567</v>
+      </c>
+    </row>
+    <row r="8" spans="8:12" x14ac:dyDescent="0.25">
+      <c r="H8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="8:12" x14ac:dyDescent="0.25">
+      <c r="H9" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I9" s="4">
+        <v>5.0299999999999997E-2</v>
+      </c>
+      <c r="J9" s="5">
+        <v>1.2873000000000001</v>
+      </c>
+      <c r="K9" s="5">
+        <v>1.2201</v>
+      </c>
+      <c r="L9" s="5">
+        <v>1.1964999999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="8:12" x14ac:dyDescent="0.25">
+      <c r="H10" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="I10" s="4">
+        <v>111</v>
+      </c>
+      <c r="J10" s="5">
+        <v>4618</v>
+      </c>
+      <c r="K10" s="5">
+        <v>4443</v>
+      </c>
+      <c r="L10" s="5">
+        <v>5870</v>
+      </c>
+    </row>
+    <row r="11" spans="8:12" x14ac:dyDescent="0.25">
+      <c r="H11" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I11">
+        <f>I9-$I$9</f>
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <f>J9-$I$9</f>
+        <v>1.2370000000000001</v>
+      </c>
+      <c r="K11">
+        <f>K9-$I$9</f>
+        <v>1.1698</v>
+      </c>
+      <c r="L11">
+        <f>L9-$I$9</f>
+        <v>1.1461999999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="8:12" x14ac:dyDescent="0.25">
+      <c r="H12" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I12">
+        <f>I10-$I$10</f>
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <f>J10-$I$10</f>
+        <v>4507</v>
+      </c>
+      <c r="K12">
+        <f t="shared" ref="K12:L12" si="2">K10-$I$10</f>
+        <v>4332</v>
+      </c>
+      <c r="L12">
+        <f t="shared" si="2"/>
+        <v>5759</v>
+      </c>
+    </row>
+    <row r="13" spans="8:12" x14ac:dyDescent="0.25">
+      <c r="H13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I13" t="s">
+        <v>7</v>
+      </c>
+      <c r="J13">
+        <f>J12/J11</f>
+        <v>3643.492320129345</v>
+      </c>
+      <c r="K13">
+        <f t="shared" ref="K13:L13" si="3">K12/K11</f>
+        <v>3703.1971277141392</v>
+      </c>
+      <c r="L13">
+        <f t="shared" si="3"/>
+        <v>5024.4285465014837</v>
+      </c>
+    </row>
+    <row r="15" spans="8:12" x14ac:dyDescent="0.25">
+      <c r="H15" t="s">
+        <v>9</v>
+      </c>
+      <c r="J15" s="3">
+        <f t="shared" ref="J15:L15" si="4">J13/J6</f>
+        <v>39.290159971394807</v>
+      </c>
+      <c r="K15" s="3">
+        <f t="shared" si="4"/>
+        <v>37.168756035912821</v>
+      </c>
+      <c r="L15" s="3">
+        <f t="shared" si="4"/>
+        <v>47.659066674421766</v>
+      </c>
+    </row>
+    <row r="16" spans="8:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20">
+        <f>AVERAGE(J6:L6)</f>
+        <v>99.263112562010846</v>
+      </c>
+      <c r="C20">
+        <f>AVERAGE(J13:L13)</f>
+        <v>4123.7059981149896</v>
+      </c>
+      <c r="D20">
+        <f>AVERAGE(J15:L15)</f>
+        <v>41.372660893909803</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23">
+        <f>STDEV(J6:L6)</f>
+        <v>6.3537629071889503</v>
+      </c>
+      <c r="C23">
+        <f>STDEV(I13:L13)</f>
+        <v>780.61962433126132</v>
+      </c>
+      <c r="D23">
+        <f>STDEV(J15:L15)</f>
+        <v>5.5465540556556432</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4AFA9B5-FC02-4247-B88A-678CD42588BF}">
+  <dimension ref="A1:D22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="4">
+        <v>5.0200000000000002E-2</v>
+      </c>
+      <c r="C2" s="4">
+        <v>1.1839</v>
+      </c>
+      <c r="D2" s="4">
+        <v>1.1863999999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="4">
+        <v>106</v>
+      </c>
+      <c r="C3" s="4">
+        <v>239</v>
+      </c>
+      <c r="D3" s="4">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <f>B2-$I$2</f>
+        <v>5.0200000000000002E-2</v>
+      </c>
+      <c r="C4">
+        <f>C2-$B$2</f>
+        <v>1.1336999999999999</v>
+      </c>
+      <c r="D4">
+        <f>D2-$B$2</f>
+        <v>1.1361999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <f>B3-$I$3</f>
+        <v>106</v>
+      </c>
+      <c r="C5">
+        <f>C3-$B$3</f>
+        <v>133</v>
+      </c>
+      <c r="D5">
+        <f>D3-$B$3</f>
+        <v>136</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6">
+        <f>C5/C4</f>
+        <v>117.31498632795272</v>
+      </c>
+      <c r="D6">
+        <f t="shared" ref="D6" si="0">D5/D4</f>
+        <v>119.69723640204191</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" s="4">
+        <v>5.0200000000000002E-2</v>
+      </c>
+      <c r="C9" s="4">
+        <v>1.2242999999999999</v>
+      </c>
+      <c r="D9" s="4">
+        <v>1.2539</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="4">
+        <v>106</v>
+      </c>
+      <c r="C10" s="4">
+        <v>10390</v>
+      </c>
+      <c r="D10" s="4">
+        <v>10584</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11">
+        <f>B9-$I$9</f>
+        <v>5.0200000000000002E-2</v>
+      </c>
+      <c r="C11">
+        <f>C9-$B$9</f>
+        <v>1.1740999999999999</v>
+      </c>
+      <c r="D11">
+        <f>D9-$B$9</f>
+        <v>1.2037</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12">
+        <f>B10-$I$10</f>
+        <v>106</v>
+      </c>
+      <c r="C12">
+        <f>C10-$B$10</f>
+        <v>10284</v>
+      </c>
+      <c r="D12">
+        <f>D10-$B$10</f>
+        <v>10478</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13">
+        <f>C12/C11</f>
+        <v>8759.0494847116952</v>
+      </c>
+      <c r="D13">
+        <f t="shared" ref="D13" si="1">D12/D11</f>
+        <v>8704.8267840824119</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="3">
+        <f t="shared" ref="C15:D15" si="2">C13/C6</f>
+        <v>74.662664667801863</v>
+      </c>
+      <c r="D15" s="3">
+        <f t="shared" si="2"/>
+        <v>72.723707294664962</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19">
+        <f>AVERAGE(C6:D6)</f>
+        <v>118.50611136499731</v>
+      </c>
+      <c r="C19">
+        <f>AVERAGE(C13:D13)</f>
+        <v>8731.9381343970526</v>
+      </c>
+      <c r="D19">
+        <f>AVERAGE(C15:D15)</f>
+        <v>73.693185981233412</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22">
+        <f>STDEV(C6:D6)</f>
+        <v>1.6845051818706183</v>
+      </c>
+      <c r="C22">
+        <f>STDEV(C13:D13)</f>
+        <v>38.341239309214288</v>
+      </c>
+      <c r="D22">
+        <f>STDEV(C15:D15)</f>
+        <v>1.3710499069767577</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>